--- a/output/StructureDefinition-BRAtestado.xlsx
+++ b/output/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:16:11-03:00</t>
+    <t>2026-08-24T11:43:54-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRAtestado.xlsx
+++ b/output/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T11:43:54-03:00</t>
+    <t>2026-09-15T15:40:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRAtestado.xlsx
+++ b/output/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:40:41-03:00</t>
+    <t>2026-09-23T09:07:03-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRAtestado.xlsx
+++ b/output/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:07:03-03:00</t>
+    <t>2026-09-30T18:22:16-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRAtestado.xlsx
+++ b/output/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:22:16-03:00</t>
+    <t>2026-10-06T15:47:25-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRAtestado.xlsx
+++ b/output/StructureDefinition-BRAtestado.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5187" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5185" uniqueCount="798">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T15:47:25-03:00</t>
+    <t>2026-10-07T20:38:46-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -996,6 +996,15 @@
     <t>gender</t>
   </si>
   <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>Sexo biológico obtido por meio de exame clínico ou de outros métodos diagnósticos referente ao indivíduo da hipótese de impossibilidade de identificação.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRSexo-1.0</t>
+  </si>
+  <si>
     <t>CarePlan.subject.extension:unidentifiedPatient.extension:gender.id</t>
   </si>
   <si>
@@ -1045,6 +1054,12 @@
   </si>
   <si>
     <t>birthYear</t>
+  </si>
+  <si>
+    <t>Ano de nascimento estimado</t>
+  </si>
+  <si>
+    <t>Estimativa do ano de nascimento por meio de observação direta da idade do indivíduo na hipótese de impossibilidade de identificação..</t>
   </si>
   <si>
     <t>CarePlan.subject.extension:unidentifiedPatient.extension:birthYear.id</t>
@@ -1067,6 +1082,15 @@
   </si>
   <si>
     <t>reason</t>
+  </si>
+  <si>
+    <t>Justificativa da impossibilidade de identificação do indivíduo</t>
+  </si>
+  <si>
+    <t>Razão pela qual não foi possível obter os dados de identificação do indivíduo no contato assistencial.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRJustificativaIndividuoNaoIdentificado-1.0</t>
   </si>
   <si>
     <t>CarePlan.subject.extension:unidentifiedPatient.extension:reason.id</t>
@@ -2408,6 +2432,10 @@
   </si>
   <si>
     <t>Allows rough dose checking.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP][classCode=SBADM].doseQuantity</t>
@@ -2802,7 +2830,7 @@
     <col min="23" max="23" width="16.40625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="15.85546875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="140.078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.34375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.20703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.2734375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.1171875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.56640625" customWidth="true" bestFit="true"/>
@@ -7189,10 +7217,10 @@
         <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7219,13 +7247,11 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>81</v>
+        <v>318</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -7272,10 +7298,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7384,10 +7410,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7498,10 +7524,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7527,13 +7553,13 @@
         <v>103</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7583,7 +7609,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>89</v>
@@ -7612,10 +7638,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7641,10 +7667,10 @@
         <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7695,7 +7721,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7724,13 +7750,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>312</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>81</v>
@@ -7755,10 +7781,10 @@
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>303</v>
+        <v>337</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7838,10 +7864,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7950,10 +7976,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8064,10 +8090,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8093,13 +8119,13 @@
         <v>103</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8107,7 +8133,7 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>81</v>
@@ -8149,7 +8175,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>89</v>
@@ -8178,10 +8204,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8204,13 +8230,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8261,7 +8287,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8290,13 +8316,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>312</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>81</v>
@@ -8321,10 +8347,10 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>302</v>
+        <v>345</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>303</v>
+        <v>346</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8351,13 +8377,11 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -8404,10 +8428,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8516,10 +8540,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8630,10 +8654,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8659,13 +8683,13 @@
         <v>103</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8673,7 +8697,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>81</v>
@@ -8715,7 +8739,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>89</v>
@@ -8744,10 +8768,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8773,10 +8797,10 @@
         <v>206</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8827,7 +8851,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8856,10 +8880,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8885,13 +8909,13 @@
         <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8899,7 +8923,7 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>81</v>
@@ -8941,7 +8965,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>89</v>
@@ -8970,10 +8994,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8996,13 +9020,13 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9053,7 +9077,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9082,10 +9106,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9111,13 +9135,13 @@
         <v>215</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9167,7 +9191,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -9176,7 +9200,7 @@
         <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>101</v>
@@ -9196,10 +9220,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9225,13 +9249,13 @@
         <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9257,13 +9281,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -9281,7 +9305,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9310,10 +9334,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9339,13 +9363,13 @@
         <v>147</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9395,7 +9419,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9413,7 +9437,7 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
@@ -9424,10 +9448,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9536,10 +9560,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9650,10 +9674,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9679,16 +9703,16 @@
         <v>109</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9716,10 +9740,10 @@
         <v>190</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -9737,7 +9761,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9755,7 +9779,7 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
@@ -9766,10 +9790,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9795,16 +9819,16 @@
         <v>206</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9829,13 +9853,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -9853,7 +9877,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9871,21 +9895,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9911,16 +9935,16 @@
         <v>103</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9933,7 +9957,7 @@
         <v>81</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>81</v>
@@ -9969,7 +9993,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9987,21 +10011,21 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10027,13 +10051,13 @@
         <v>215</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10047,7 +10071,7 @@
         <v>81</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>81</v>
@@ -10083,7 +10107,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10101,21 +10125,21 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10138,13 +10162,13 @@
         <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10195,7 +10219,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10213,21 +10237,21 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10250,16 +10274,16 @@
         <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10309,7 +10333,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10327,21 +10351,21 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10367,13 +10391,13 @@
         <v>215</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10423,7 +10447,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10452,10 +10476,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10478,16 +10502,16 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10537,7 +10561,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10552,28 +10576,28 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10592,19 +10616,19 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -10653,7 +10677,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10668,28 +10692,28 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10708,13 +10732,13 @@
         <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10765,7 +10789,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10780,13 +10804,13 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -10794,10 +10818,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10820,16 +10844,16 @@
         <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10879,7 +10903,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10894,13 +10918,13 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -10908,10 +10932,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10934,16 +10958,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10993,7 +11017,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11022,10 +11046,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11048,17 +11072,17 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>81</v>
@@ -11107,7 +11131,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11122,13 +11146,13 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -11136,10 +11160,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11162,19 +11186,19 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -11223,7 +11247,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11238,24 +11262,24 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11364,10 +11388,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11478,10 +11502,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11507,13 +11531,13 @@
         <v>215</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11563,7 +11587,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11572,7 +11596,7 @@
         <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>101</v>
@@ -11592,10 +11616,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11621,13 +11645,13 @@
         <v>103</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11653,13 +11677,13 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -11677,7 +11701,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11706,10 +11730,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11735,13 +11759,13 @@
         <v>147</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11791,7 +11815,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11809,7 +11833,7 @@
         <v>81</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>81</v>
@@ -11820,10 +11844,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11932,10 +11956,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12046,10 +12070,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12075,16 +12099,16 @@
         <v>109</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12112,10 +12136,10 @@
         <v>190</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -12133,7 +12157,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12151,7 +12175,7 @@
         <v>81</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>81</v>
@@ -12162,10 +12186,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12191,16 +12215,16 @@
         <v>206</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -12225,13 +12249,13 @@
         <v>81</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
@@ -12249,7 +12273,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12267,21 +12291,21 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12307,16 +12331,16 @@
         <v>103</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -12329,7 +12353,7 @@
         <v>81</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>81</v>
@@ -12365,7 +12389,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12383,21 +12407,21 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12423,13 +12447,13 @@
         <v>215</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12443,7 +12467,7 @@
         <v>81</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>81</v>
@@ -12479,7 +12503,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12497,21 +12521,21 @@
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12534,13 +12558,13 @@
         <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12591,7 +12615,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12609,21 +12633,21 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12646,16 +12670,16 @@
         <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12705,7 +12729,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12723,21 +12747,21 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12763,13 +12787,13 @@
         <v>215</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12819,7 +12843,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12848,10 +12872,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12874,19 +12898,19 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -12935,7 +12959,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12950,7 +12974,7 @@
         <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>81</v>
@@ -12964,10 +12988,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12990,19 +13014,19 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13051,7 +13075,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13069,21 +13093,21 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13106,17 +13130,17 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -13165,7 +13189,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13177,13 +13201,13 @@
         <v>81</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
@@ -13194,10 +13218,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13306,10 +13330,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13420,14 +13444,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13449,10 +13473,10 @@
         <v>135</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>138</v>
@@ -13507,7 +13531,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13536,10 +13560,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13565,13 +13589,13 @@
         <v>206</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13597,13 +13621,13 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
@@ -13621,7 +13645,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13650,10 +13674,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13676,19 +13700,19 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -13737,7 +13761,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13752,10 +13776,10 @@
         <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
@@ -13766,10 +13790,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13792,19 +13816,19 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>81</v>
@@ -13853,7 +13877,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13871,21 +13895,21 @@
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13908,19 +13932,19 @@
         <v>81</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -13969,7 +13993,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13978,16 +14002,16 @@
         <v>89</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
@@ -13998,10 +14022,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14024,17 +14048,17 @@
         <v>81</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
@@ -14083,7 +14107,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14092,7 +14116,7 @@
         <v>89</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>101</v>
@@ -14101,7 +14125,7 @@
         <v>81</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
@@ -14112,10 +14136,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14224,10 +14248,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14338,14 +14362,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14367,10 +14391,10 @@
         <v>135</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>138</v>
@@ -14425,7 +14449,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14454,10 +14478,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14483,14 +14507,14 @@
         <v>109</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -14518,10 +14542,10 @@
         <v>190</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
@@ -14539,7 +14563,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14557,7 +14581,7 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>81</v>
@@ -14568,10 +14592,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14594,17 +14618,17 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="L104" t="s" s="2">
         <v>158</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -14653,7 +14677,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14682,10 +14706,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14714,13 +14738,13 @@
         <v>163</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>165</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -14769,7 +14793,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14798,10 +14822,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14827,16 +14851,16 @@
         <v>206</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>81</v>
@@ -14861,13 +14885,13 @@
         <v>81</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>81</v>
@@ -14885,7 +14909,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14900,24 +14924,24 @@
         <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>586</v>
+        <v>594</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14943,13 +14967,13 @@
         <v>206</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14975,13 +14999,13 @@
         <v>81</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
@@ -14999,7 +15023,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15014,7 +15038,7 @@
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>81</v>
@@ -15028,10 +15052,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15054,16 +15078,16 @@
         <v>81</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15113,7 +15137,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15128,7 +15152,7 @@
         <v>101</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>81</v>
@@ -15142,10 +15166,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15168,17 +15192,17 @@
         <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>81</v>
@@ -15227,7 +15251,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15245,7 +15269,7 @@
         <v>81</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>81</v>
@@ -15256,10 +15280,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15285,23 +15309,23 @@
         <v>109</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>81</v>
@@ -15322,10 +15346,10 @@
         <v>190</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>81</v>
@@ -15343,7 +15367,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>89</v>
@@ -15358,24 +15382,24 @@
         <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>613</v>
+        <v>621</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15401,13 +15425,13 @@
         <v>206</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15457,7 +15481,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15472,7 +15496,7 @@
         <v>101</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>81</v>
@@ -15486,10 +15510,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15515,22 +15539,22 @@
         <v>267</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q112" t="s" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="R112" t="s" s="2">
         <v>81</v>
@@ -15575,7 +15599,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15590,10 +15614,10 @@
         <v>101</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>81</v>
@@ -15604,10 +15628,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15630,17 +15654,17 @@
         <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -15689,7 +15713,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15704,24 +15728,24 @@
         <v>101</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>632</v>
+        <v>640</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15830,10 +15854,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15944,14 +15968,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15973,10 +15997,10 @@
         <v>135</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>138</v>
@@ -16031,7 +16055,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16060,10 +16084,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16086,17 +16110,17 @@
         <v>90</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
@@ -16145,7 +16169,7 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16163,7 +16187,7 @@
         <v>81</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>81</v>
@@ -16174,10 +16198,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16200,17 +16224,17 @@
         <v>90</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>81</v>
@@ -16259,7 +16283,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16271,13 +16295,13 @@
         <v>81</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>81</v>
@@ -16288,10 +16312,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16400,10 +16424,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16514,10 +16538,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16540,13 +16564,13 @@
         <v>90</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16597,7 +16621,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16615,7 +16639,7 @@
         <v>81</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>81</v>
@@ -16626,10 +16650,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16652,19 +16676,19 @@
         <v>90</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>81</v>
@@ -16713,7 +16737,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16731,7 +16755,7 @@
         <v>81</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>81</v>
@@ -16742,10 +16766,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16768,13 +16792,13 @@
         <v>90</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16825,7 +16849,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16843,7 +16867,7 @@
         <v>81</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>81</v>
@@ -16854,10 +16878,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16880,19 +16904,19 @@
         <v>90</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -16941,7 +16965,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16959,7 +16983,7 @@
         <v>81</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>81</v>
@@ -16970,10 +16994,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16996,19 +17020,19 @@
         <v>90</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17057,7 +17081,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17075,7 +17099,7 @@
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>81</v>
@@ -17086,10 +17110,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17115,10 +17139,10 @@
         <v>109</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17148,10 +17172,10 @@
         <v>190</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>81</v>
@@ -17169,7 +17193,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17187,7 +17211,7 @@
         <v>81</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>81</v>
@@ -17198,10 +17222,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17224,13 +17248,13 @@
         <v>90</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -17238,7 +17262,7 @@
         <v>81</v>
       </c>
       <c r="Q127" t="s" s="2">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="R127" t="s" s="2">
         <v>81</v>
@@ -17283,7 +17307,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17301,7 +17325,7 @@
         <v>81</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>81</v>
@@ -17312,10 +17336,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17338,13 +17362,13 @@
         <v>90</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17395,7 +17419,7 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17413,7 +17437,7 @@
         <v>81</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>81</v>
@@ -17424,10 +17448,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17450,13 +17474,13 @@
         <v>90</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17507,7 +17531,7 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17525,7 +17549,7 @@
         <v>81</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>81</v>
@@ -17536,10 +17560,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17562,13 +17586,13 @@
         <v>90</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17619,7 +17643,7 @@
         <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17637,7 +17661,7 @@
         <v>81</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>81</v>
@@ -17648,10 +17672,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17677,10 +17701,10 @@
         <v>109</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17710,10 +17734,10 @@
         <v>190</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>81</v>
@@ -17731,7 +17755,7 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17749,7 +17773,7 @@
         <v>81</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>81</v>
@@ -17760,10 +17784,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17789,13 +17813,13 @@
         <v>109</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -17825,7 +17849,7 @@
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>81</v>
@@ -17843,7 +17867,7 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17872,10 +17896,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17898,16 +17922,16 @@
         <v>90</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17957,7 +17981,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -17986,10 +18010,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18015,16 +18039,16 @@
         <v>109</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>81</v>
@@ -18052,10 +18076,10 @@
         <v>190</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>81</v>
@@ -18073,7 +18097,7 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18091,7 +18115,7 @@
         <v>81</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>81</v>
@@ -18102,10 +18126,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18128,13 +18152,13 @@
         <v>90</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18185,7 +18209,7 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18203,7 +18227,7 @@
         <v>81</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>81</v>
@@ -18214,10 +18238,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18243,13 +18267,13 @@
         <v>206</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18278,10 +18302,10 @@
         <v>113</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>81</v>
@@ -18299,7 +18323,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18317,7 +18341,7 @@
         <v>81</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>81</v>
@@ -18328,10 +18352,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18354,19 +18378,19 @@
         <v>81</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>81</v>
@@ -18415,7 +18439,7 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18433,21 +18457,21 @@
         <v>81</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>750</v>
+        <v>758</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18470,19 +18494,19 @@
         <v>81</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>81</v>
@@ -18531,7 +18555,7 @@
         <v>81</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18546,24 +18570,24 @@
         <v>101</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>758</v>
+        <v>766</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18586,13 +18610,13 @@
         <v>81</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18619,13 +18643,13 @@
         <v>81</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>81</v>
@@ -18643,7 +18667,7 @@
         <v>81</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -18661,25 +18685,25 @@
         <v>81</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>766</v>
+        <v>774</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18698,17 +18722,17 @@
         <v>81</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>81</v>
@@ -18757,7 +18781,7 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18769,27 +18793,27 @@
         <v>81</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>101</v>
+        <v>781</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>773</v>
+        <v>782</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>774</v>
+        <v>783</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18812,13 +18836,13 @@
         <v>81</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>776</v>
+        <v>785</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18869,7 +18893,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -18881,27 +18905,27 @@
         <v>81</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>101</v>
+        <v>781</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>779</v>
+        <v>788</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18927,10 +18951,10 @@
         <v>215</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>782</v>
+        <v>791</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -18981,7 +19005,7 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -18999,21 +19023,21 @@
         <v>81</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19036,17 +19060,17 @@
         <v>81</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>785</v>
+        <v>794</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>786</v>
+        <v>795</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>787</v>
+        <v>796</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>81</v>
@@ -19095,7 +19119,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19110,16 +19134,16 @@
         <v>101</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>

--- a/output/StructureDefinition-BRAtestado.xlsx
+++ b/output/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T20:38:46-03:00</t>
+    <t>2026-10-08T20:36:58-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRAtestado.xlsx
+++ b/output/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:36:58-03:00</t>
+    <t>2026-10-14T17:05:02-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRAtestado.xlsx
+++ b/output/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T17:05:02-03:00</t>
+    <t>2026-10-19T10:41:45-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRAtestado.xlsx
+++ b/output/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T10:41:45-03:00</t>
+    <t>2026-10-20T16:57:20-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRAtestado.xlsx
+++ b/output/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:57:20-03:00</t>
+    <t>2026-10-21T08:58:18-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRAtestado.xlsx
+++ b/output/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T08:58:18-03:00</t>
+    <t>2026-10-21T11:27:45-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRAtestado.xlsx
+++ b/output/StructureDefinition-BRAtestado.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:27:45-03:00</t>
+    <t>2026-10-21T12:30:11-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
